--- a/metadata/pituitary_epigenomics.xlsx
+++ b/metadata/pituitary_epigenomics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/georgiagoddard/Desktop/Research_Project/TF_mapping/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63DB5A5-704C-8041-8CF4-31030953A3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FEE006-B987-6B4C-A3A2-838B487E3566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2020" windowWidth="28800" windowHeight="15980" xr2:uid="{E7683E52-20A2-44C9-985B-23DBE75FE055}"/>
+    <workbookView xWindow="940" yWindow="2120" windowWidth="28800" windowHeight="15980" xr2:uid="{E7683E52-20A2-44C9-985B-23DBE75FE055}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -7756,7 +7756,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>431</v>
       </c>
@@ -7879,7 +7879,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>441</v>
       </c>
@@ -8330,7 +8330,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>478</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>483</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>508</v>
       </c>
@@ -10234,7 +10234,7 @@
   <autoFilter ref="A1:M186" xr:uid="{F1897EC6-11F5-4A91-A5F3-BA3053A976EB}">
     <filterColumn colId="6">
       <filters>
-        <filter val="TPIT"/>
+        <filter val="Lbt2"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/metadata/pituitary_epigenomics.xlsx
+++ b/metadata/pituitary_epigenomics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/georgiagoddard/Desktop/Research_Project/TF_mapping/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FEE006-B987-6B4C-A3A2-838B487E3566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70E7A77-CE90-4947-96AE-E1C52D2A7024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="2120" windowWidth="28800" windowHeight="15980" xr2:uid="{E7683E52-20A2-44C9-985B-23DBE75FE055}"/>
+    <workbookView xWindow="7900" yWindow="1640" windowWidth="22840" windowHeight="16000" xr2:uid="{E7683E52-20A2-44C9-985B-23DBE75FE055}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -8330,7 +8330,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>478</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>483</v>
       </c>
@@ -9132,7 +9132,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="157" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B157" t="s">
         <v>545</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="161" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B161" t="s">
         <v>556</v>
       </c>
@@ -10234,7 +10234,7 @@
   <autoFilter ref="A1:M186" xr:uid="{F1897EC6-11F5-4A91-A5F3-BA3053A976EB}">
     <filterColumn colId="6">
       <filters>
-        <filter val="Lbt2"/>
+        <filter val="PIT1"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/metadata/pituitary_epigenomics.xlsx
+++ b/metadata/pituitary_epigenomics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/georgiagoddard/Desktop/Research_Project/TF_mapping/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70E7A77-CE90-4947-96AE-E1C52D2A7024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE1E4EB-63C1-0E45-A72D-39983EB3C102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7900" yWindow="1640" windowWidth="22840" windowHeight="16000" xr2:uid="{E7683E52-20A2-44C9-985B-23DBE75FE055}"/>
+    <workbookView xWindow="44180" yWindow="5140" windowWidth="33000" windowHeight="20900" xr2:uid="{E7683E52-20A2-44C9-985B-23DBE75FE055}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -3984,7 +3984,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>114</v>
       </c>
@@ -4025,7 +4025,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>118</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>121</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>151</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>154</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>157</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>205</v>
       </c>
@@ -5173,7 +5173,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>212</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>216</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>222</v>
       </c>
@@ -5337,7 +5337,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>225</v>
       </c>
@@ -5419,7 +5419,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>231</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>234</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>240</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>243</v>
       </c>
@@ -6321,7 +6321,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>308</v>
       </c>
@@ -6362,7 +6362,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>312</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>315</v>
       </c>
@@ -6444,7 +6444,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>319</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>322</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>326</v>
       </c>
@@ -6567,7 +6567,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>330</v>
       </c>
@@ -6608,7 +6608,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>335</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>339</v>
       </c>
@@ -6772,7 +6772,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="99" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>349</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>353</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>356</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>360</v>
       </c>
@@ -6936,7 +6936,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>363</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>367</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>370</v>
       </c>
@@ -7059,7 +7059,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="106" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>373</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="107" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>376</v>
       </c>
@@ -7141,7 +7141,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="108" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>380</v>
       </c>
@@ -7182,7 +7182,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>383</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="110" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>386</v>
       </c>
@@ -7264,7 +7264,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>389</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>392</v>
       </c>
@@ -7346,7 +7346,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>396</v>
       </c>
@@ -7633,7 +7633,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>421</v>
       </c>
@@ -7674,7 +7674,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>425</v>
       </c>
@@ -7715,7 +7715,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>428</v>
       </c>
@@ -7756,7 +7756,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>431</v>
       </c>
@@ -7879,7 +7879,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>441</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>444</v>
       </c>
@@ -7961,7 +7961,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>447</v>
       </c>
@@ -8002,7 +8002,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>450</v>
       </c>
@@ -8043,7 +8043,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>453</v>
       </c>
@@ -8084,7 +8084,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>456</v>
       </c>
@@ -8125,7 +8125,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>459</v>
       </c>
@@ -8248,7 +8248,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>469</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>475</v>
       </c>
@@ -8412,7 +8412,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>486</v>
       </c>
@@ -8456,7 +8456,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>494</v>
       </c>
@@ -8588,7 +8588,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>504</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>508</v>
       </c>
@@ -9512,7 +9512,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="167" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>568</v>
       </c>
@@ -9553,7 +9553,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="168" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>576</v>
       </c>
@@ -10154,7 +10154,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="185" spans="2:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B185" t="s">
         <v>616</v>
       </c>
@@ -10192,7 +10192,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="186" spans="2:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B186" t="s">
         <v>619</v>
       </c>
@@ -10232,9 +10232,36 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:M186" xr:uid="{F1897EC6-11F5-4A91-A5F3-BA3053A976EB}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="ChIP"/>
+        <filter val="CR"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="6">
       <filters>
+        <filter val="Ascl1"/>
+        <filter val="Ash2"/>
+        <filter val="CTCF"/>
+        <filter val="ctrl"/>
+        <filter val="FLAG"/>
+        <filter val="FOXO1"/>
+        <filter val="GR"/>
+        <filter val="H3"/>
+        <filter val="IgG"/>
+        <filter val="Input"/>
+        <filter val="Ldb1"/>
+        <filter val="NEUROD1"/>
+        <filter val="p300"/>
+        <filter val="PAX7"/>
         <filter val="PIT1"/>
+        <filter val="Prop1"/>
+        <filter val="Protein_A"/>
+        <filter val="SMAD2"/>
+        <filter val="SMC1"/>
+        <filter val="SOX2"/>
+        <filter val="STAT3"/>
+        <filter val="TPIT"/>
       </filters>
     </filterColumn>
   </autoFilter>
